--- a/EXCEL/Exercise Files/Chapter04/04_05_Binomial.xlsx
+++ b/EXCEL/Exercise Files/Chapter04/04_05_Binomial.xlsx
@@ -1,22 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25407"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Curtis\Desktop\Exercise Files\Chapter04\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\neha work\Data Analytics\EXCEL\Exercise Files\Chapter04\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{955DFC1F-0B2A-4061-948C-D0D7A4B90C1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{129BC9BF-A1E1-4772-B688-77ED2688A3F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="12549" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="288" yWindow="324" windowWidth="22752" windowHeight="11916" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Binomial" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="125725" concurrentCalc="0"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
       <mx:ArchID Flags="2"/>
     </ext>
@@ -44,9 +53,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="168" formatCode="0.0000000%"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="0.0000000%"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -97,19 +106,19 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -133,7 +142,7 @@
         <name val="Calibri"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="168" formatCode="0.0000000%"/>
+      <numFmt numFmtId="166" formatCode="0.0000000%"/>
     </dxf>
     <dxf>
       <font>
@@ -345,67 +354,67 @@
                 <c:formatCode>0.0000000%</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>1.8124545836334979E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>2.1331196253532715E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>1.2117706710340171E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>4.4375603446451709E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>0.1181965594387069</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>0.24539574514843887</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>0.41662541821923227</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>0.60102660460316426</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>0.76237764268910391</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>0.87821941362259914</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>0.94683338563705388</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>0.9804206446651087</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>0.99398473004182319</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>0.99847933821398893</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v>0.99968942502957203</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0</c:v>
+                  <c:v>0.99995005911292834</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0</c:v>
+                  <c:v>0.99999391580964692</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0</c:v>
+                  <c:v>0.99999947231420849</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0</c:v>
+                  <c:v>0.99999997097487436</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0</c:v>
+                  <c:v>0.99999999923904159</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1199,7 +1208,9 @@
   <autoFilter ref="A4:B25" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Successes"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Percentage of Outcomes" dataDxfId="0" dataCellStyle="Percent"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Percentage of Outcomes" dataDxfId="0" dataCellStyle="Percent">
+      <calculatedColumnFormula>_xlfn.BINOM.DIST(Table1[[#This Row],[Successes]],$B$2,$B$1,TRUE)</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1528,13 +1539,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultColWidth="8.84375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.3828125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1543,7 +1554,7 @@
       </c>
       <c r="G1" s="2"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -1551,10 +1562,10 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B3" s="1"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>2</v>
       </c>
@@ -1562,172 +1573,193 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>0</v>
       </c>
       <c r="B5" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+        <f>_xlfn.BINOM.DIST(Table1[[#This Row],[Successes]],$B$2,$B$1,TRUE)</f>
+        <v>1.8124545836334979E-4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
       <c r="B6" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+        <f>_xlfn.BINOM.DIST(Table1[[#This Row],[Successes]],$B$2,$B$1,TRUE)</f>
+        <v>2.1331196253532715E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2</v>
       </c>
       <c r="B7" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+        <f>_xlfn.BINOM.DIST(Table1[[#This Row],[Successes]],$B$2,$B$1,TRUE)</f>
+        <v>1.2117706710340171E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>3</v>
       </c>
       <c r="B8" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+        <f>_xlfn.BINOM.DIST(Table1[[#This Row],[Successes]],$B$2,$B$1,TRUE)</f>
+        <v>4.4375603446451709E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>4</v>
       </c>
       <c r="B9" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+        <f>_xlfn.BINOM.DIST(Table1[[#This Row],[Successes]],$B$2,$B$1,TRUE)</f>
+        <v>0.1181965594387069</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>5</v>
       </c>
       <c r="B10" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+        <f>_xlfn.BINOM.DIST(Table1[[#This Row],[Successes]],$B$2,$B$1,TRUE)</f>
+        <v>0.24539574514843887</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>6</v>
       </c>
       <c r="B11" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+        <f>_xlfn.BINOM.DIST(Table1[[#This Row],[Successes]],$B$2,$B$1,TRUE)</f>
+        <v>0.41662541821923227</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>7</v>
       </c>
       <c r="B12" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+        <f>_xlfn.BINOM.DIST(Table1[[#This Row],[Successes]],$B$2,$B$1,TRUE)</f>
+        <v>0.60102660460316426</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>8</v>
       </c>
       <c r="B13" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+        <f>_xlfn.BINOM.DIST(Table1[[#This Row],[Successes]],$B$2,$B$1,TRUE)</f>
+        <v>0.76237764268910391</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>9</v>
       </c>
       <c r="B14" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+        <f>_xlfn.BINOM.DIST(Table1[[#This Row],[Successes]],$B$2,$B$1,TRUE)</f>
+        <v>0.87821941362259914</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>10</v>
       </c>
       <c r="B15" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+        <f>_xlfn.BINOM.DIST(Table1[[#This Row],[Successes]],$B$2,$B$1,TRUE)</f>
+        <v>0.94683338563705388</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>11</v>
       </c>
       <c r="B16" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+        <f>_xlfn.BINOM.DIST(Table1[[#This Row],[Successes]],$B$2,$B$1,TRUE)</f>
+        <v>0.9804206446651087</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>12</v>
       </c>
       <c r="B17" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
+        <f>_xlfn.BINOM.DIST(Table1[[#This Row],[Successes]],$B$2,$B$1,TRUE)</f>
+        <v>0.99398473004182319</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>13</v>
       </c>
       <c r="B18" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
+        <f>_xlfn.BINOM.DIST(Table1[[#This Row],[Successes]],$B$2,$B$1,TRUE)</f>
+        <v>0.99847933821398893</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>14</v>
       </c>
       <c r="B19" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
+        <f>_xlfn.BINOM.DIST(Table1[[#This Row],[Successes]],$B$2,$B$1,TRUE)</f>
+        <v>0.99968942502957203</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>15</v>
       </c>
       <c r="B20" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
+        <f>_xlfn.BINOM.DIST(Table1[[#This Row],[Successes]],$B$2,$B$1,TRUE)</f>
+        <v>0.99995005911292834</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>16</v>
       </c>
       <c r="B21" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
+        <f>_xlfn.BINOM.DIST(Table1[[#This Row],[Successes]],$B$2,$B$1,TRUE)</f>
+        <v>0.99999391580964692</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>17</v>
       </c>
       <c r="B22" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
+        <f>_xlfn.BINOM.DIST(Table1[[#This Row],[Successes]],$B$2,$B$1,TRUE)</f>
+        <v>0.99999947231420849</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>18</v>
       </c>
       <c r="B23" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
+        <f>_xlfn.BINOM.DIST(Table1[[#This Row],[Successes]],$B$2,$B$1,TRUE)</f>
+        <v>0.99999997097487436</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>19</v>
       </c>
       <c r="B24" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
+        <f>_xlfn.BINOM.DIST(Table1[[#This Row],[Successes]],$B$2,$B$1,TRUE)</f>
+        <v>0.99999999923904159</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>20</v>
       </c>
       <c r="B25" s="6">
-        <v>0</v>
+        <f>_xlfn.BINOM.DIST(Table1[[#This Row],[Successes]],$B$2,$B$1,TRUE)</f>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
